--- a/measurements/26/Filled_2D_sections/sagittal/week26_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/sagittal/week26_sagittal_Batch_Allmarks.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O24"/>
+  <dimension ref="A1:Z27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,12 +487,67 @@
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Metric</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Mean</t>
         </is>
@@ -506,17 +561,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5.031231409875074</v>
+        <v>1917.800453514739</v>
       </c>
       <c r="D2" t="n">
-        <v>9.749933039269797</v>
+        <v>190.3558355286008</v>
       </c>
       <c r="E2" t="n">
-        <v>9.43949592985758</v>
+        <v>184.2949205353146</v>
       </c>
       <c r="F2" t="n">
         <v>1.032887043092025</v>
@@ -525,15 +580,45 @@
         <v>0.6650907242271511</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I2" t="n">
+        <v>1.646205357142857</v>
+      </c>
+      <c r="J2" t="n">
+        <v>8.489583333333332</v>
+      </c>
+      <c r="K2" t="n">
+        <v>4.489707341269841</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>8.489583333333332</v>
+      </c>
+      <c r="R2" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.646205357142857</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>area</t>
         </is>
       </c>
-      <c r="O2" s="2" t="n">
-        <v>4.923735871505057</v>
+      <c r="Z2" s="2" t="n">
+        <v>1876.825396825397</v>
       </c>
     </row>
     <row r="3">
@@ -544,34 +629,64 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>5.413444378346223</v>
+        <v>2063.492063492063</v>
       </c>
       <c r="D3" t="n">
-        <v>9.967711881893438</v>
+        <v>194.6077081703004</v>
       </c>
       <c r="E3" t="n">
-        <v>9.744014987131445</v>
+        <v>190.2402926058996</v>
       </c>
       <c r="F3" t="n">
         <v>1.022957363577275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.68468780168167</v>
+        <v>0.6846878016816698</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I3" t="n">
+        <v>1.813616071428571</v>
+      </c>
+      <c r="J3" t="n">
+        <v>7.5390625</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4.389260912698412</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>7.5390625</v>
+      </c>
+      <c r="R3" t="n">
+        <v>3.815104166666667</v>
+      </c>
+      <c r="S3" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1.813616071428571</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>perimeter</t>
         </is>
       </c>
-      <c r="O3" s="2" t="n">
-        <v>10.55631672783596</v>
+      <c r="Z3" s="2" t="n">
+        <v>206.0995170672734</v>
       </c>
     </row>
     <row r="4">
@@ -582,34 +697,64 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.613920285544319</v>
+        <v>2139.909297052154</v>
       </c>
       <c r="D4" t="n">
-        <v>10.30427261678184</v>
+        <v>201.1786558514549</v>
       </c>
       <c r="E4" t="n">
-        <v>9.999753565323063</v>
+        <v>195.2332838944026</v>
       </c>
       <c r="F4" t="n">
         <v>1.030452655604912</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6644180546860966</v>
+        <v>0.6644180546860967</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
+        <v>3</v>
+      </c>
+      <c r="I4" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="J4" t="n">
+        <v>7.589285714285714</v>
+      </c>
+      <c r="K4" t="n">
+        <v>4.989459325396825</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>7.589285714285714</v>
+      </c>
+      <c r="R4" t="n">
+        <v>5.531994047619047</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1.847098214285714</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>perimeter_convex</t>
         </is>
       </c>
-      <c r="O4" s="2" t="n">
-        <v>9.526920785264272</v>
+      <c r="Z4" s="2" t="n">
+        <v>186.0017867599215</v>
       </c>
     </row>
     <row r="5">
@@ -620,33 +765,60 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.74330755502677</v>
+        <v>2189.22902494331</v>
       </c>
       <c r="D5" t="n">
-        <v>10.70390125600303</v>
+        <v>208.9809292838687</v>
       </c>
       <c r="E5" t="n">
-        <v>10.28161571083999</v>
+        <v>200.7363067354475</v>
       </c>
       <c r="F5" t="n">
         <v>1.041071905140144</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6299234113208577</v>
+        <v>0.6299234113208576</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I5" t="n">
+        <v>7.464657738095237</v>
+      </c>
+      <c r="J5" t="n">
+        <v>8.305431547619047</v>
+      </c>
+      <c r="K5" t="n">
+        <v>7.885044642857142</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.305431547619047</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7.464657738095237</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
         <is>
           <t>LGI</t>
         </is>
       </c>
-      <c r="O5" s="2" t="n">
+      <c r="Z5" s="2" t="n">
         <v>1.112547508321149</v>
       </c>
     </row>
@@ -658,42 +830,60 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>5.546698393813207</v>
+        <v>2114.285714285714</v>
       </c>
       <c r="D6" t="n">
-        <v>11.74114299692759</v>
+        <v>229.2318394638243</v>
       </c>
       <c r="E6" t="n">
-        <v>10.37672535384574</v>
+        <v>202.5932092893691</v>
       </c>
       <c r="F6" t="n">
         <v>1.131488267883681</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5056193204361231</v>
+        <v>0.505619320436123</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8646150914634146</v>
+        <v>7.87016369047619</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8646150914634146</v>
+        <v>16.88058035714286</v>
       </c>
       <c r="K6" t="n">
-        <v>0.8646150914634146</v>
-      </c>
-      <c r="N6" t="inlineStr">
+        <v>12.37537202380952</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" t="n">
+        <v>16.88058035714286</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>7.87016369047619</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Compactness</t>
         </is>
       </c>
-      <c r="O6" s="2" t="n">
+      <c r="Z6" s="2" t="n">
         <v>0.5623710973204241</v>
       </c>
     </row>
@@ -705,17 +895,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>5.426829268292683</v>
+        <v>2068.59410430839</v>
       </c>
       <c r="D7" t="n">
-        <v>11.44254203831277</v>
+        <v>223.4020112242017</v>
       </c>
       <c r="E7" t="n">
-        <v>10.28508247398749</v>
+        <v>200.8039911588033</v>
       </c>
       <c r="F7" t="n">
         <v>1.112537703732826</v>
@@ -727,21 +917,36 @@
         <v>1</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8498475609756098</v>
+        <v>16.59226190476191</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8498475609756098</v>
+        <v>16.59226190476191</v>
       </c>
       <c r="K7" t="n">
-        <v>0.8498475609756098</v>
-      </c>
-      <c r="N7" t="inlineStr">
+        <v>16.59226190476191</v>
+      </c>
+      <c r="L7" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" t="n">
+        <v>16.59226190476191</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Sulci_count</t>
         </is>
       </c>
-      <c r="O7" s="2" t="n">
-        <v>0.45</v>
+      <c r="Z7" s="2" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="8">
@@ -752,43 +957,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5.23051754907793</v>
+        <v>1993.764172335601</v>
       </c>
       <c r="D8" t="n">
-        <v>12.11709945376326</v>
+        <v>236.5719417163304</v>
       </c>
       <c r="E8" t="n">
-        <v>10.3254935101765</v>
+        <v>201.5929685320173</v>
       </c>
       <c r="F8" t="n">
-        <v>1.17351286326615</v>
+        <v>1.173512863266149</v>
       </c>
       <c r="G8" t="n">
-        <v>0.4476691660096559</v>
+        <v>0.4476691660096561</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.9141577743902439</v>
+        <v>17.84784226190476</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9141577743902439</v>
+        <v>17.84784226190476</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9141577743902439</v>
-      </c>
-      <c r="N8" t="inlineStr">
+        <v>17.84784226190476</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" t="n">
+        <v>17.84784226190476</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>min_depth_mm</t>
         </is>
       </c>
-      <c r="O8" s="2" t="n">
-        <v>0.8242610941734417</v>
+      <c r="Z8" s="2" t="n">
+        <v>6.432942708333333</v>
       </c>
     </row>
     <row r="9">
@@ -799,34 +1019,61 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.268590124925639</v>
+        <v>1627.097505668934</v>
       </c>
       <c r="D9" t="n">
-        <v>9.250292045314138</v>
+        <v>180.6009399323236</v>
       </c>
       <c r="E9" t="n">
-        <v>8.578185968282746</v>
+        <v>167.4788689045679</v>
       </c>
       <c r="F9" t="n">
         <v>1.078350606936765</v>
       </c>
       <c r="G9" t="n">
-        <v>0.6268785803772889</v>
+        <v>0.6268785803772891</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4.828869047619047</v>
+      </c>
+      <c r="J9" t="n">
+        <v>9.512648809523808</v>
+      </c>
+      <c r="K9" t="n">
+        <v>7.170758928571428</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" t="n">
+        <v>9.512648809523808</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>4.828869047619047</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
         <is>
           <t>max_depth_mm</t>
         </is>
       </c>
-      <c r="O9" s="2" t="n">
-        <v>0.8242610941734417</v>
+      <c r="Z9" s="2" t="n">
+        <v>11.86356026785714</v>
       </c>
     </row>
     <row r="10">
@@ -837,17 +1084,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>3.954788816180845</v>
+        <v>1507.482993197279</v>
       </c>
       <c r="D10" t="n">
-        <v>8.951691031455994</v>
+        <v>174.7711106141408</v>
       </c>
       <c r="E10" t="n">
-        <v>8.279584954424603</v>
+        <v>161.6490395863851</v>
       </c>
       <c r="F10" t="n">
         <v>1.081176300591278</v>
@@ -856,15 +1103,42 @@
         <v>0.6201874779216172</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
+        <v>2</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.860491071428571</v>
+      </c>
+      <c r="J10" t="n">
+        <v>9.730282738095237</v>
+      </c>
+      <c r="K10" t="n">
+        <v>7.295386904761904</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" t="n">
+        <v>9.730282738095237</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.860491071428571</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
         <is>
           <t>mean_depth_mm</t>
         </is>
       </c>
-      <c r="O10" s="2" t="n">
-        <v>0.8242610941734417</v>
+      <c r="Z10" s="2" t="n">
+        <v>9.017097594246032</v>
       </c>
     </row>
     <row r="11">
@@ -875,17 +1149,17 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.669839381320643</v>
+        <v>1017.687074829932</v>
       </c>
       <c r="D11" t="n">
-        <v>10.10915063357935</v>
+        <v>197.3691314175015</v>
       </c>
       <c r="E11" t="n">
-        <v>7.313780583986422</v>
+        <v>142.7928590206873</v>
       </c>
       <c r="F11" t="n">
         <v>1.382205894406158</v>
@@ -894,16 +1168,45 @@
         <v>0.3282960542649889</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7317073170731707</v>
+        <v>7.01078869047619</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7317073170731707</v>
+        <v>14.28571428571428</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7317073170731707</v>
+        <v>10.1593501984127</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>14.28571428571428</v>
+      </c>
+      <c r="N11" t="n">
+        <v>9.181547619047619</v>
+      </c>
+      <c r="O11" t="n">
+        <v>7.01078869047619</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="12">
@@ -914,35 +1217,64 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.993158834027365</v>
+        <v>1140.92970521542</v>
       </c>
       <c r="D12" t="n">
-        <v>10.14854634389645</v>
+        <v>198.1382857617878</v>
       </c>
       <c r="E12" t="n">
-        <v>7.75627169957975</v>
+        <v>151.4319712775094</v>
       </c>
       <c r="F12" t="n">
         <v>1.308431000998368</v>
       </c>
       <c r="G12" t="n">
-        <v>0.3652009924079419</v>
+        <v>0.365200992407942</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I12" t="n">
-        <v>0.6696836890243902</v>
+        <v>5.433407738095238</v>
       </c>
       <c r="J12" t="n">
-        <v>0.6696836890243902</v>
+        <v>13.07477678571428</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6696836890243902</v>
+        <v>8.829985119047619</v>
+      </c>
+      <c r="L12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M12" t="n">
+        <v>13.07477678571428</v>
+      </c>
+      <c r="N12" t="n">
+        <v>7.981770833333333</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.433407738095238</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>Primary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="n">
+        <v>14.39871651785714</v>
       </c>
     </row>
     <row r="13">
@@ -953,17 +1285,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>3.973527662105889</v>
+        <v>1514.625850340136</v>
       </c>
       <c r="D13" t="n">
-        <v>8.917197997977095</v>
+        <v>174.0976751986004</v>
       </c>
       <c r="E13" t="n">
-        <v>8.302241831291013</v>
+        <v>162.0913881347293</v>
       </c>
       <c r="F13" t="n">
         <v>1.074071097804971</v>
@@ -972,7 +1304,42 @@
         <v>0.6279561021934478</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.319940476190476</v>
+      </c>
+      <c r="J13" t="n">
+        <v>8.707217261904761</v>
+      </c>
+      <c r="K13" t="n">
+        <v>7.013578869047619</v>
+      </c>
+      <c r="L13" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" t="n">
+        <v>8.707217261904761</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>5.319940476190476</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>Primary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="n">
+        <v>8.581659226190476</v>
       </c>
     </row>
     <row r="14">
@@ -983,35 +1350,61 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4.943783462224866</v>
+        <v>1884.467120181406</v>
       </c>
       <c r="D14" t="n">
-        <v>12.53101562581411</v>
+        <v>244.6531622182755</v>
       </c>
       <c r="E14" t="n">
-        <v>9.940152325281282</v>
+        <v>194.0696406364441</v>
       </c>
       <c r="F14" t="n">
         <v>1.260646237175195</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3956368736145581</v>
+        <v>0.3956368736145582</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9067263719512195</v>
+        <v>9.066220238095237</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9067263719512195</v>
+        <v>17.70275297619047</v>
       </c>
       <c r="K14" t="n">
-        <v>0.9067263719512195</v>
+        <v>13.38448660714286</v>
+      </c>
+      <c r="L14" t="n">
+        <v>1</v>
+      </c>
+      <c r="M14" t="n">
+        <v>17.70275297619047</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>9.066220238095237</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>Primary_v3_mm</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="n">
+        <v>7.01078869047619</v>
       </c>
     </row>
     <row r="15">
@@ -1022,17 +1415,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.223973825104105</v>
+        <v>1991.269841269841</v>
       </c>
       <c r="D15" t="n">
-        <v>11.65440279099999</v>
+        <v>227.538340205238</v>
       </c>
       <c r="E15" t="n">
-        <v>10.10669931260551</v>
+        <v>197.3212722937266</v>
       </c>
       <c r="F15" t="n">
         <v>1.153136393052094</v>
@@ -1041,16 +1434,42 @@
         <v>0.4833155950718603</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8657583841463415</v>
+        <v>1.248139880952381</v>
       </c>
       <c r="J15" t="n">
-        <v>0.8657583841463415</v>
+        <v>16.90290178571428</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8657583841463415</v>
+        <v>9.075520833333332</v>
+      </c>
+      <c r="L15" t="n">
+        <v>1</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16.90290178571428</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.248139880952381</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="n">
+        <v>1.1</v>
       </c>
     </row>
     <row r="16">
@@ -1061,35 +1480,58 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5.39649018441404</v>
+        <v>2057.02947845805</v>
       </c>
       <c r="D16" t="n">
-        <v>11.81258041974975</v>
+        <v>230.626570099876</v>
       </c>
       <c r="E16" t="n">
-        <v>10.18997283388929</v>
+        <v>198.947088661648</v>
       </c>
       <c r="F16" t="n">
         <v>1.159235712627621</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4859948857599116</v>
+        <v>0.4859948857599115</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8277439024390244</v>
+        <v>16.16071428571428</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8277439024390244</v>
+        <v>16.16071428571428</v>
       </c>
       <c r="K16" t="n">
-        <v>0.8277439024390244</v>
+        <v>16.16071428571428</v>
+      </c>
+      <c r="L16" t="n">
+        <v>1</v>
+      </c>
+      <c r="M16" t="n">
+        <v>16.16071428571428</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>Secondary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="n">
+        <v>7.337921626984127</v>
       </c>
     </row>
     <row r="17">
@@ -1100,35 +1542,61 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>5.509518143961928</v>
+        <v>2100.113378684807</v>
       </c>
       <c r="D17" t="n">
-        <v>11.43070590496063</v>
+        <v>223.1709248111361</v>
       </c>
       <c r="E17" t="n">
-        <v>10.3506017719827</v>
+        <v>202.0831774529956</v>
       </c>
       <c r="F17" t="n">
         <v>1.104351819997711</v>
       </c>
       <c r="G17" t="n">
-        <v>0.5298798190787223</v>
+        <v>0.5298798190787224</v>
       </c>
       <c r="H17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0.788109756097561</v>
+        <v>8.203125</v>
       </c>
       <c r="J17" t="n">
-        <v>0.788109756097561</v>
+        <v>15.38690476190476</v>
       </c>
       <c r="K17" t="n">
-        <v>0.788109756097561</v>
+        <v>11.79501488095238</v>
+      </c>
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15.38690476190476</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>8.203125</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>Secondary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="n">
+        <v>5.34890518707483</v>
       </c>
     </row>
     <row r="18">
@@ -1139,17 +1607,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.689767995240929</v>
+        <v>2168.820861678004</v>
       </c>
       <c r="D18" t="n">
-        <v>10.48510709041502</v>
+        <v>204.7092336700076</v>
       </c>
       <c r="E18" t="n">
-        <v>10.18650611435495</v>
+        <v>198.8794050897871</v>
       </c>
       <c r="F18" t="n">
         <v>1.029313385051552</v>
@@ -1158,7 +1626,42 @@
         <v>0.6503672759096997</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="I18" t="n">
+        <v>7.472098214285714</v>
+      </c>
+      <c r="J18" t="n">
+        <v>8.463541666666666</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.96781994047619</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>8.463541666666666</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7.472098214285714</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="n">
+        <v>0.45</v>
       </c>
     </row>
     <row r="19">
@@ -1169,17 +1672,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.553242117787032</v>
+        <v>2116.780045351474</v>
       </c>
       <c r="D19" t="n">
-        <v>10.17466996355755</v>
+        <v>198.6483183361235</v>
       </c>
       <c r="E19" t="n">
-        <v>9.959342479705811</v>
+        <v>194.4443055561611</v>
       </c>
       <c r="F19" t="n">
         <v>1.021620652597349</v>
@@ -1188,7 +1691,45 @@
         <v>0.6740867817580034</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="I19" t="n">
+        <v>1.223958333333333</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.659970238095237</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.877232142857143</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>7.659970238095237</v>
+      </c>
+      <c r="R19" t="n">
+        <v>5.747767857142857</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1.223958333333333</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Tertiary_v1_mm</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>1.739742772108843</v>
       </c>
     </row>
     <row r="20">
@@ -1199,26 +1740,67 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5.334027364663891</v>
+        <v>2033.219954648526</v>
       </c>
       <c r="D20" t="n">
-        <v>9.945055002119483</v>
+        <v>194.1653595651899</v>
       </c>
       <c r="E20" t="n">
-        <v>9.689316432650497</v>
+        <v>189.1723684469859</v>
       </c>
       <c r="F20" t="n">
         <v>1.026393871151448</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6777206592858426</v>
+        <v>0.6777206592858427</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="J20" t="n">
+        <v>7.403273809523809</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.536086309523809</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>7.403273809523809</v>
+      </c>
+      <c r="R20" t="n">
+        <v>4.077380952380953</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.54203869047619</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Tertiary_v2_mm</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>1.374627976190476</v>
       </c>
     </row>
     <row r="21">
@@ -1229,17 +1811,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>not_full_slice</t>
+          <t>sagittal</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>4.958060678167757</v>
+        <v>1889.909297052154</v>
       </c>
       <c r="D21" t="n">
-        <v>9.689316423927865</v>
+        <v>189.1723682766869</v>
       </c>
       <c r="E21" t="n">
-        <v>9.433577866089054</v>
+        <v>184.1793773855482</v>
       </c>
       <c r="F21" t="n">
         <v>1.027109391735464</v>
@@ -1248,6 +1830,44 @@
         <v>0.6636443842159535</v>
       </c>
       <c r="H21" t="n">
+        <v>3</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.627604166666667</v>
+      </c>
+      <c r="J21" t="n">
+        <v>9.036458333333332</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.507068452380952</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>9.036458333333332</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.857142857142857</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.627604166666667</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1258,7 +1878,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02439024390243903</v>
+        <v>0.4761904761904762</v>
       </c>
     </row>
     <row r="23">
@@ -1281,6 +1901,38 @@
       </c>
       <c r="B24" t="n">
         <v>25</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ScalebarMeasuredPixels:</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldLength:</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ScalebarRealWorldUnit:</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/measurements/26/Filled_2D_sections/sagittal/week26_sagittal_Batch_Allmarks.xlsx
+++ b/measurements/26/Filled_2D_sections/sagittal/week26_sagittal_Batch_Allmarks.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Analysis" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -137,6 +138,211 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>15</col>
+      <colOff>0</colOff>
+      <row>67</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>24</col>
+      <colOff>0</colOff>
+      <row>45</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="4953000" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>35</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5905500" cy="3429000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1938,4 +2144,1277 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Workbook Analysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Workbook</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>week26_sagittal_Batch_Allmarks.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Week</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Axis</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sagittal</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Slice rows analyzed</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>When a sulcus class count exceeds 3, approximate raw sulcus values are reconstructed from count + min/max/mean for summary stats and boxplots.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Core Metric Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>area</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>20</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1876.825396825397</v>
+      </c>
+      <c r="D10" t="n">
+        <v>338.9421889101619</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1017.687074829932</v>
+      </c>
+      <c r="F10" t="n">
+        <v>2189.22902494331</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>perimeter</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C11" t="n">
+        <v>206.0995170672734</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20.89608226070263</v>
+      </c>
+      <c r="E11" t="n">
+        <v>174.0976751986004</v>
+      </c>
+      <c r="F11" t="n">
+        <v>244.6531622182755</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LGI</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>20</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1.112547508321149</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1027929503847089</v>
+      </c>
+      <c r="E12" t="n">
+        <v>1.021620652597349</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1.382205894406158</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Compactness</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>20</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.5623710973204241</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.1144295193359657</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.3282960542649889</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.6846878016816698</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Counts Per Slice</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>File</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sulci_count</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Primary_count</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Secondary_count</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Tertiary_count</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Unclassified_count</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>band_axis0_s00_idx0083.png</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>band_axis0_s01_idx0087.png</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0</v>
+      </c>
+      <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>band_axis0_s02_idx0090.png</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>2</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>band_axis0_s03_idx0094.png</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>2</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
+        <v>2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>band_axis0_s04_idx0097.png</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+      <c r="C21" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>band_axis0_s05_idx0100.png</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>band_axis0_s06_idx0104.png</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>band_axis0_s07_idx0107.png</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G24" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>band_axis0_s08_idx0110.png</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>band_axis0_s09_idx0114.png</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>band_axis0_s10_idx0117.png</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3</v>
+      </c>
+      <c r="C27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" t="n">
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>1</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>band_axis0_s11_idx0121.png</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" t="n">
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>1</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>band_axis0_s12_idx0124.png</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>band_axis0_s13_idx0127.png</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" t="n">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>band_axis0_s14_idx0131.png</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>band_axis0_s15_idx0134.png</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+      <c r="C32" t="n">
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>band_axis0_s16_idx0137.png</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>band_axis0_s17_idx0141.png</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>3</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>3</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" t="n">
+        <v>2</v>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>band_axis0_s18_idx0144.png</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>4</v>
+      </c>
+      <c r="C35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="n">
+        <v>4</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>band_axis0_s19_idx0148.png</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>3</v>
+      </c>
+      <c r="C36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" t="n">
+        <v>3</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="n">
+        <v>2</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Rounded Sulcus Count Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Sulci_count_rounded</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>20</v>
+      </c>
+      <c r="C40" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0.8013147091860318</v>
+      </c>
+      <c r="E40" t="n">
+        <v>1</v>
+      </c>
+      <c r="F40" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Primary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>20</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0.7863975156570492</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0</v>
+      </c>
+      <c r="F41" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Secondary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>20</v>
+      </c>
+      <c r="C42" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0.7880689256524124</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Tertiary_count_rounded</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>20</v>
+      </c>
+      <c r="C43" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6863327411532597</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Unclassified_count_rounded</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>20</v>
+      </c>
+      <c r="C44" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Sulcus Value Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>metric</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>mean</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>std</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>min</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>max</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>primary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>15</v>
+      </c>
+      <c r="C48" t="n">
+        <v>13.13058035714286</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3.989434018990411</v>
+      </c>
+      <c r="E48" t="n">
+        <v>7.01078869047619</v>
+      </c>
+      <c r="F48" t="n">
+        <v>17.84784226190476</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>secondary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>22</v>
+      </c>
+      <c r="C49" t="n">
+        <v>6.70505275974026</v>
+      </c>
+      <c r="D49" t="n">
+        <v>1.784429967614964</v>
+      </c>
+      <c r="E49" t="n">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="F49" t="n">
+        <v>9.066220238095237</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>tertiary_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>9</v>
+      </c>
+      <c r="C50" t="n">
+        <v>1.658606150793651</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0.5191906826430914</v>
+      </c>
+      <c r="E50" t="n">
+        <v>1.121651785714286</v>
+      </c>
+      <c r="F50" t="n">
+        <v>2.857142857142857</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>unclassified_sulcus_values</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>